--- a/familyhub-sg-home-inventory-example.xlsx
+++ b/familyhub-sg-home-inventory-example.xlsx
@@ -365,7 +365,7 @@
     <t xml:space="preserve">IMG_0121.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Christmas decorations</t>
+    <t xml:space="preserve">Camping tent and gear</t>
   </si>
   <si>
     <t xml:space="preserve">Box 2</t>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B30" s="13" t="n">
         <f aca="false">COUNTIF(Inventory!$B$2:$B$300,A30)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">SUMIFS(Inventory!$H$2:$H$300,Inventory!$B$2:$B$300,A30)</f>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B31" s="13" t="n">
         <f aca="false">COUNTIF(Inventory!$B$2:$B$300,A31)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="15" t="n">
         <f aca="false">SUMIFS(Inventory!$H$2:$H$300,Inventory!$B$2:$B$300,A31)</f>
@@ -1987,7 +1987,7 @@
         <v>112</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>35</v>
